--- a/sheets/조재수대금교본/검수/옛사랑.xlsx
+++ b/sheets/조재수대금교본/검수/옛사랑.xlsx
@@ -4343,11 +4343,7 @@
     </row>
     <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B11" s="21"/>
       <c r="C11" s="22"/>
       <c r="D11" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/옛사랑.xlsx
+++ b/sheets/조재수대금교본/검수/옛사랑.xlsx
@@ -3941,19 +3941,19 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
